--- a/backend/templates/PurchaseOrder-STD.xlsx
+++ b/backend/templates/PurchaseOrder-STD.xlsx
@@ -1,25 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0460A62C-9D89-404A-9734-3A2FFE043A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2400" windowHeight="585"/>
   </bookViews>
   <sheets>
-    <sheet name="ZRH含税" sheetId="5" r:id="rId1"/>
+    <sheet sheetId="5" name="ZRH含税" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase">ZRH含税!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ZRH含税!$A$1:$I$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ZRH含税'!$A1:$I32</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <r>
       <t xml:space="preserve">东莞市智锐恒电子有限公司
@@ -28,9 +26,9 @@
     <r>
       <rPr>
         <b/>
+        <charset val="134"/>
         <sz val="18"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> 采   购   单</t>
     </r>
@@ -69,6 +67,9 @@
     <t>品名规格</t>
   </si>
   <si>
+    <t>材质</t>
+  </si>
+  <si>
     <t>表面处理/颜色</t>
   </si>
   <si>
@@ -104,9 +105,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>、货款结算：</t>
     </r>
@@ -117,9 +118,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>以上单价以人民币结算；</t>
     </r>
@@ -130,9 +131,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>付款方式：月结；</t>
     </r>
@@ -143,9 +144,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>、品质：</t>
     </r>
@@ -156,9 +157,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>产品生产按我司的工程图或合格样品及所规定之要求进行生产加工；</t>
     </r>
@@ -169,9 +170,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>检验方法：我司分为全检和抽检两种方式，抽检按MIL-STD-105E二级正常单次抽样计划表进行检验</t>
     </r>
@@ -182,25 +183,25 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>：</t>
     </r>
     <r>
       <rPr>
+        <family val="2"/>
         <sz val="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
       </rPr>
       <t>CR=0  MAJ=0.4  MIN=1.0</t>
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>；</t>
     </r>
@@ -211,9 +212,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>、其它：</t>
     </r>
@@ -224,9 +225,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>供应商在收到我司订单后，应在两天内及时回签，否则视为默认；</t>
     </r>
@@ -237,9 +238,9 @@
     </r>
     <r>
       <rPr>
+        <charset val="134"/>
         <sz val="9"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>交货时请在送货单上注明订单号码、产品编号、产品名称，在卸货时按我司仓管的要求对产品进行合理摆放；</t>
     </r>
@@ -260,91 +261,91 @@
     <r>
       <rPr>
         <u/>
+        <charset val="134"/>
         <sz val="12"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">              </t>
     </r>
     <r>
       <rPr>
         <u/>
+        <charset val="134"/>
+        <color indexed="9"/>
         <sz val="12"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>制表：</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <charset val="134"/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">    袁小琼     </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <charset val="134"/>
         <color indexed="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
       </rPr>
       <t>1</t>
     </r>
   </si>
   <si>
     <r>
-      <t>制表：</t>
+      <t xml:space="preserve"> 经  办  人：</t>
     </r>
     <r>
       <rPr>
         <u/>
+        <charset val="134"/>
         <sz val="12"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">    袁小琼     </t>
+      </rPr>
+      <t xml:space="preserve">              </t>
     </r>
     <r>
       <rPr>
         <u/>
+        <charset val="134"/>
+        <color indexed="9"/>
         <sz val="12"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">1   </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>审核：</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <charset val="134"/>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+      </rPr>
+      <t xml:space="preserve">               </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <charset val="134"/>
         <color indexed="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> 经  办  人：</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
         <sz val="12"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">              </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color indexed="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">1   </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>审核：</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">               </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color indexed="9"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
       </rPr>
       <t>1</t>
     </r>
@@ -353,125 +354,99 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="177" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="178" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="179" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00_);[Red](#,##0.00)"/>
+    <numFmt numFmtId="165" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;¥&quot;#,##0.00_);[Red](&quot;¥&quot;#,##0.00)"/>
+    <numFmt numFmtId="167" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="20"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <charset val="134"/>
       <sz val="14"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="8"/>
       <name val="MS Sans Serif"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <charset val="134"/>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -488,7 +463,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -558,18 +533,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -585,24 +552,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -610,17 +564,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -628,12 +594,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -646,7 +618,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -658,7 +630,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -670,6 +642,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -679,16 +657,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -700,7 +681,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -709,10 +690,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -721,51 +705,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1047,434 +992,605 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultRowHeight="18.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="5.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11" style="2" customWidth="1"/>
+    <col min="3" max="3" width="7" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="5.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="51" t="s">
+    <row r="1" ht="54" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-    </row>
-    <row r="2" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="52" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" ht="17.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-    </row>
-    <row r="3" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="53" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" ht="17.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-    </row>
-    <row r="4" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" ht="17.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="5"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="49" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-    </row>
-    <row r="5" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="48" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" ht="17.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="49" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-    </row>
-    <row r="6" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="48" t="s">
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" ht="17.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="49" t="s">
+      <c r="B6" s="13"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-    </row>
-    <row r="7" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="50" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" ht="17.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-    </row>
-    <row r="8" spans="1:9" s="11" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="12" t="s">
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" ht="27.95" customHeight="1" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="17" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="42" t="s">
+      <c r="J8" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-    </row>
-    <row r="11" spans="1:9" s="20" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="42" t="s">
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:10" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10" ht="20.1" customHeight="1" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="43"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-    </row>
-    <row r="12" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="26" t="s">
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+    </row>
+    <row r="11" ht="20.1" customHeight="1" spans="1:10" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28"/>
-    </row>
-    <row r="13" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="27" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="29"/>
-    </row>
-    <row r="14" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="27" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="29"/>
-    </row>
-    <row r="15" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="27" t="s">
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="29"/>
-    </row>
-    <row r="16" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="27" t="s">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="29"/>
-    </row>
-    <row r="17" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="27" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="26"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="29"/>
-    </row>
-    <row r="18" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="27" t="s">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="29"/>
-    </row>
-    <row r="19" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="27" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="29"/>
-    </row>
-    <row r="20" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="27" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="29"/>
-    </row>
-    <row r="21" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="27" t="s">
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="29"/>
-    </row>
-    <row r="22" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="27" t="s">
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="29"/>
-    </row>
-    <row r="23" spans="1:9" s="30" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="31" t="s">
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" ht="12" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
-    </row>
-    <row r="24" spans="1:9" s="30" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-    </row>
-    <row r="25" spans="1:9" s="30" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="34"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-    </row>
-    <row r="26" spans="1:9" s="30" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-    </row>
-    <row r="27" spans="1:9" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="41" t="s">
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" ht="12" customHeight="1" spans="1:10" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="47" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="39"/>
+    </row>
+    <row r="24" ht="6.95" customHeight="1" spans="1:10" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="39"/>
+    </row>
+    <row r="25" ht="6.95" customHeight="1" spans="1:10" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="39"/>
+    </row>
+    <row r="26" ht="6.95" customHeight="1" spans="1:10" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="39"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-    </row>
-    <row r="28" spans="1:9" s="2" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" spans="1:9" s="2" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="36" t="s">
+      <c r="B27" s="46"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="G29" s="41" t="s">
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+    </row>
+    <row r="28" ht="6" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="48"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" ht="29.1" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-    </row>
-    <row r="30" spans="1:9" s="2" customFormat="1" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="36" t="s">
+      <c r="B29" s="2"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="G30" s="41" t="s">
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+    </row>
+    <row r="30" ht="29.1" customHeight="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-    </row>
-    <row r="31" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="39"/>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="40"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+    </row>
+    <row r="31" ht="18.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="49"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="G2:J2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="H30:J30"/>
   </mergeCells>
-  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>